--- a/product_upload/packages/38/file.xlsx
+++ b/product_upload/packages/38/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -852,6 +857,11 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>FEMAPLEX 2.5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-2E1DDC66B6AE</t>
         </is>
       </c>
@@ -875,7 +885,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1046,6 +1056,11 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>ELOCOM 0.1% OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-8D860CAAAE25</t>
         </is>
       </c>
@@ -1069,7 +1084,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1240,6 +1255,11 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>DIPROSALIC OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-7CA691ECE5C5</t>
         </is>
       </c>
@@ -1263,7 +1283,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1434,6 +1454,11 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>ELOCOM 0.1% CREAM</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-8D8A25A976F4</t>
         </is>
       </c>
@@ -1457,7 +1482,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1624,6 +1649,11 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>IRBEGEN PLUS 300/12.5 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-9F62DC16DC53</t>
         </is>
       </c>
@@ -1647,7 +1677,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1806,6 +1836,11 @@
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>SPEDRA 200 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-9DDFF3E15C2A</t>
         </is>
       </c>
@@ -1829,7 +1864,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1992,6 +2027,11 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>PANREST 20 mg Enteric Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-7C5EF7807A60</t>
         </is>
       </c>
@@ -2015,7 +2055,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2174,6 +2214,11 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>PANREST 40 mg Enteric Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-84444F391CEF</t>
         </is>
       </c>
@@ -2197,7 +2242,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2370,6 +2415,11 @@
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>DENACIF 300 mg Capsule</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-E780223294EB</t>
         </is>
       </c>
@@ -2393,7 +2443,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2562,6 +2612,11 @@
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>DENACIF 125 mg/5 ml Suspension</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-CACA7946907E</t>
         </is>
       </c>
@@ -2585,7 +2640,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2762,6 +2817,11 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>DENACIF 125 mg/5 ml Suspension</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-17C2E7929EF8</t>
         </is>
       </c>
@@ -2785,7 +2845,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2948,6 +3008,11 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>QUET 100 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-D63751314DDD</t>
         </is>
       </c>
@@ -2971,7 +3036,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3130,6 +3195,11 @@
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>QUET 200 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-41805EF612D3</t>
         </is>
       </c>
@@ -3153,7 +3223,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3316,6 +3386,11 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>LUXAT 10mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-AF0E4A7086A4</t>
         </is>
       </c>
@@ -3339,7 +3414,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3510,6 +3585,11 @@
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>PAFINUR 10 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-D54F3ED482CC</t>
         </is>
       </c>
@@ -3533,7 +3613,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3692,6 +3772,11 @@
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>STEROFUNDIN ISO Solution For Infusion</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-724602C0D49E</t>
         </is>
       </c>
@@ -3715,7 +3800,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3874,6 +3959,11 @@
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>STEROFUNDIN ISO Solution For Infusion</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-1BC336AC86F7</t>
         </is>
       </c>
@@ -3897,7 +3987,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4056,6 +4146,11 @@
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>SERCAND 200 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-395803193291</t>
         </is>
       </c>
@@ -4079,7 +4174,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4246,6 +4341,11 @@
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>XYRIO 20 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-C25CAD89DAC4</t>
         </is>
       </c>
@@ -4269,7 +4369,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4440,6 +4540,11 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>ZORON 4 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-60FF9003C2EC</t>
         </is>
       </c>
@@ -4463,7 +4568,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4634,6 +4739,11 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>ZORON 8 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-16B6C2FB8117</t>
         </is>
       </c>
@@ -4657,7 +4767,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4816,6 +4926,11 @@
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>SERCAND 100 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-EFA275640E4C</t>
         </is>
       </c>
@@ -4839,7 +4954,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4994,6 +5109,11 @@
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>SERCAND 300 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-B7E722FC8ECF</t>
         </is>
       </c>
@@ -5017,7 +5137,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5176,6 +5296,11 @@
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>SUPRANE LIQUID FOR INHALATION</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-964EEC58D636</t>
         </is>
       </c>
@@ -5199,7 +5324,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5360,6 +5485,11 @@
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>MIDIANA 3 mg/ 0.3 mg F.C.tablet</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-807B45746F92</t>
         </is>
       </c>
@@ -5383,7 +5513,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5542,6 +5672,11 @@
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>DAPO 60 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-4D77E2CCC5C0</t>
         </is>
       </c>
@@ -5565,7 +5700,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5732,6 +5867,11 @@
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>XYRIO 5 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-87858AAD6BFC</t>
         </is>
       </c>
@@ -5755,7 +5895,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5914,6 +6054,11 @@
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>DIFLUCAN 200 mg capsule</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-5C76835EA48C</t>
         </is>
       </c>
@@ -5937,7 +6082,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6096,6 +6241,11 @@
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>DIFLUCAN 50 mg capsule</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-77D45963231A</t>
         </is>
       </c>
@@ -6119,7 +6269,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6286,6 +6436,11 @@
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>DALACIN C 300MG CAPS</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-71D21B07A5D9</t>
         </is>
       </c>
@@ -6309,7 +6464,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6476,6 +6631,11 @@
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>DALACIN C 150 MG CAPS</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-EAA6634FFCD8</t>
         </is>
       </c>
@@ -6499,7 +6659,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6670,6 +6830,11 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>CLAZ MR 30 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-DC346595AA8A</t>
         </is>
       </c>
@@ -6693,7 +6858,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6860,6 +7025,11 @@
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>DIFLUCAN 150 mg capsule</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-CDA52829BDD8</t>
         </is>
       </c>
@@ -6883,7 +7053,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7042,6 +7212,11 @@
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>LIVADOR 750MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-DA59821E3201</t>
         </is>
       </c>
@@ -7065,7 +7240,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7232,6 +7407,11 @@
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>METOJECT 50 mg/ml solution for injection</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-DB9B2B4E36A2</t>
         </is>
       </c>
@@ -7255,7 +7435,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7418,6 +7598,11 @@
       </c>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>SEIZET 100 mg Chewable/Dispersible Tablet</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-2C8C74F34CB6</t>
         </is>
       </c>
@@ -7441,7 +7626,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7604,6 +7789,11 @@
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>VIAGRA 50 mg Orodispersible Tablet</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-847C3E1D27FC</t>
         </is>
       </c>
@@ -7627,7 +7817,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7790,6 +7980,11 @@
       </c>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>ZEIMER 10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-3947FA8D3261</t>
         </is>
       </c>
@@ -7813,7 +8008,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7984,6 +8179,11 @@
       </c>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>Xelorni 8 mg F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-D57A2962A5A9</t>
         </is>
       </c>
@@ -8007,7 +8207,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8182,6 +8382,11 @@
       </c>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>ENNLA 5% Cream</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-9DC2DC04ED22</t>
         </is>
       </c>
@@ -8205,7 +8410,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8368,6 +8573,11 @@
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>ENNLA 5% Cream</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-A8D9C1376639</t>
         </is>
       </c>
@@ -8391,7 +8601,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8566,6 +8776,11 @@
       </c>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>ENNLA 5% Cream</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-CC551FEAAF61</t>
         </is>
       </c>
@@ -8589,7 +8804,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8756,6 +8971,11 @@
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>METOJECT 50 mg/ml solution for injection</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-169CCF68851F</t>
         </is>
       </c>
@@ -8779,7 +8999,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8938,6 +9158,11 @@
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>TARGINACT 10MG/5MG PR TABLET</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-1FCC3B5CE7FA</t>
         </is>
       </c>
@@ -8961,7 +9186,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9118,6 +9343,11 @@
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>OBSOL 5 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-A6D8A6F275D5</t>
         </is>
       </c>
@@ -9141,7 +9371,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9312,6 +9542,11 @@
       </c>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>TRELEGY ELLIPTA 100/62.5/25MCG Inhalation powder, pre-dispensed</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-DDECFC9BF7EC</t>
         </is>
       </c>
@@ -9335,7 +9570,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9502,6 +9737,11 @@
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>GAMCET 0.4MG PROLONGED RELEASE F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-F5D1D88E1F3C</t>
         </is>
       </c>
@@ -9525,7 +9765,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9700,6 +9940,11 @@
       </c>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>VIAGRA 50 mg Orodispersible Tablet</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-BA6743F12A94</t>
         </is>
       </c>
@@ -9723,7 +9968,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9886,6 +10131,11 @@
       </c>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>QUREX XL 1000 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-8F1D057DB29F</t>
         </is>
       </c>
@@ -9909,7 +10159,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10064,6 +10314,11 @@
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>LIVADOR 500 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-6B5B8882A1B3</t>
         </is>
       </c>
@@ -10087,7 +10342,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10250,6 +10505,11 @@
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>ROLITAC 5 mg Capsule</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-97BFC30CC433</t>
         </is>
       </c>
@@ -10273,7 +10533,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10440,6 +10700,11 @@
       </c>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>ROLITAC 0.5 mg Capsule</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-07E449AA685E</t>
         </is>
       </c>
@@ -10463,7 +10728,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10622,6 +10887,11 @@
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>AXE BRAND UNIVERSAL OIL</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-89753991877D</t>
         </is>
       </c>
@@ -10645,7 +10915,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10808,6 +11078,11 @@
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>ROLITAC 1 mg Capsule</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-4F4AC015162C</t>
         </is>
       </c>
@@ -10831,7 +11106,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -10998,6 +11273,11 @@
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>Xevaneer 300 mg capsule</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-5C5431C64A31</t>
         </is>
       </c>
@@ -11021,7 +11301,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11180,6 +11460,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>METOJECT 50 mg/ml solution for injection</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-8FD288A1CCFA</t>
         </is>
       </c>
@@ -11203,7 +11488,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11358,6 +11643,11 @@
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>TARGINACT 20MG/10MG PR TABLET</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-146020FA7944</t>
         </is>
       </c>
@@ -11381,7 +11671,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11540,6 +11830,11 @@
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>ANASTROZOLE 1MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-3D05E10DC485</t>
         </is>
       </c>
@@ -11563,7 +11858,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11744,6 +12039,11 @@
       </c>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>ZYPREXA 5MG COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-A2F766A3D645</t>
         </is>
       </c>
@@ -11767,7 +12067,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11938,6 +12238,11 @@
       </c>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>XEVANEER 125mg/5ml Powder For Oral Suspension</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-D1D87B406971</t>
         </is>
       </c>
@@ -11961,7 +12266,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12126,6 +12431,11 @@
       </c>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>OBSOL 10 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-3CB185B7553E</t>
         </is>
       </c>
@@ -12149,7 +12459,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12312,6 +12622,11 @@
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>REVCOX 200MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-0F9EEC0955DF</t>
         </is>
       </c>
@@ -12335,7 +12650,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12498,6 +12813,11 @@
       </c>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>TARGINACT 40MG/20MG PR TABLET</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-5B66A362A783</t>
         </is>
       </c>
@@ -12521,7 +12841,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12694,6 +13014,11 @@
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>ZYPREXA 10MG F.C.TAB</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-023DF92D6CF4</t>
         </is>
       </c>
@@ -12717,7 +13042,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12884,6 +13209,11 @@
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>ANORO ELLIPTA</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-091AAE925888</t>
         </is>
       </c>
@@ -12907,7 +13237,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13074,6 +13404,11 @@
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>IMIGRAN 20 MG NASAL SPRAY</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-0BB5B70DF227</t>
         </is>
       </c>
@@ -13097,7 +13432,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13260,6 +13595,11 @@
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>WELLBUTRIN XL 300 EXTENDED RELEASE F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-FC58F8100460</t>
         </is>
       </c>
@@ -13283,7 +13623,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13454,6 +13794,11 @@
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>WELLBUTRIN XL 150 EXTENDED RELEASE F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-78708AB8211D</t>
         </is>
       </c>
@@ -13477,7 +13822,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13644,6 +13989,11 @@
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>VOLIBRIS 5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-41446F40DA8C</t>
         </is>
       </c>
@@ -13667,7 +14017,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13838,6 +14188,11 @@
       </c>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>VOLIBRIS 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-B82341A89C95</t>
         </is>
       </c>
@@ -13861,7 +14216,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -14032,6 +14387,11 @@
       </c>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>RELVAR ELLIPTA</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-B7C5DB12AA7D</t>
         </is>
       </c>
@@ -14055,7 +14415,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14226,6 +14586,11 @@
       </c>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>RELVAR ELLIPTA 200/25 mcg inhalation powder</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-4F9A36413049</t>
         </is>
       </c>
@@ -14249,7 +14614,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14416,6 +14781,11 @@
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>FUCITHALMIC VISCOUS EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-ACF7E73E2307</t>
         </is>
       </c>
@@ -14439,7 +14809,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14602,6 +14972,11 @@
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>DESCOVY 200MG/25MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-5C59C0DD8A8C</t>
         </is>
       </c>
@@ -14625,7 +15000,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14792,6 +15167,11 @@
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>RAFOL 1 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-32E656878B21</t>
         </is>
       </c>
@@ -14815,7 +15195,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14980,6 +15360,11 @@
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>DIOZAD</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-0BFEE343B215</t>
         </is>
       </c>
@@ -15003,7 +15388,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15170,6 +15555,11 @@
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>PYRIDOXIN TAB 40MG</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-17971AA45D52</t>
         </is>
       </c>
@@ -15193,7 +15583,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15356,6 +15746,11 @@
       </c>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>ALZAMED 5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-A6E3E93B4C20</t>
         </is>
       </c>
@@ -15379,7 +15774,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15556,6 +15951,11 @@
       </c>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>HEXAXIM VACCINE</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-ECC68CAD4575</t>
         </is>
       </c>
@@ -15579,7 +15979,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15746,6 +16146,11 @@
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>VIZOL 0.4% EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-95F07AEACF84</t>
         </is>
       </c>
@@ -15769,7 +16174,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15936,6 +16341,11 @@
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>ETHIONAMIDE 250 MG FCT</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-328EE5612DEF</t>
         </is>
       </c>
@@ -15959,7 +16369,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16118,6 +16528,11 @@
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>LATUDA 40 MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-168ACD3ED824</t>
         </is>
       </c>
@@ -16141,7 +16556,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16296,6 +16711,11 @@
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>LETRASAN 2.5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-E9154BAA471F</t>
         </is>
       </c>
@@ -16319,7 +16739,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16482,6 +16902,11 @@
       </c>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>ELNASO 0.05% NASAL SPRAY</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-A8093073AB80</t>
         </is>
       </c>
@@ -16505,7 +16930,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16672,6 +17097,11 @@
       </c>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>DESLORATADINE-GLENMARK 5MG TAB</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-C77B47B766AD</t>
         </is>
       </c>
@@ -16695,7 +17125,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16854,6 +17284,11 @@
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>TORLEN 5 MG FILM-COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-5B4BA4F69CEB</t>
         </is>
       </c>
@@ -16877,7 +17312,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -17032,6 +17467,11 @@
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>NEULASTIM 6MG-0.6ML PRE-FILLED SYRINGE</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-0653E5AD7A9D</t>
         </is>
       </c>
@@ -17055,7 +17495,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17222,6 +17662,11 @@
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>NAVELA 1.5 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-F42D46B3395C</t>
         </is>
       </c>
@@ -17245,7 +17690,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17422,6 +17867,11 @@
       </c>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>APROVASC 150MG/5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-DB196309556F</t>
         </is>
       </c>
@@ -17445,7 +17895,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17616,6 +18066,11 @@
       </c>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>IBICAR 250 MCG INHALATION</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-CF81B4E1A2D8</t>
         </is>
       </c>
@@ -17639,7 +18094,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17808,6 +18263,11 @@
       </c>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>ANADEX 1MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-391463B3D697</t>
         </is>
       </c>
@@ -17831,7 +18291,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -17994,6 +18454,11 @@
       </c>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>RESINCALCIO POWDER FOR SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-B073DF209051</t>
         </is>
       </c>
@@ -18017,7 +18482,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18180,6 +18645,11 @@
       </c>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>CARBAGLU 200MG DISPERSIBLE TABLETS</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-211E65B71192</t>
         </is>
       </c>
@@ -18203,7 +18673,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18378,6 +18848,11 @@
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>SKINOREN 20% CREAM</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-F887592A389B</t>
         </is>
       </c>
@@ -18401,7 +18876,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18564,6 +19039,11 @@
       </c>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>KYTRIL 1MG TAB</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-81AB373CE4CC</t>
         </is>
       </c>
@@ -18587,7 +19067,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18756,6 +19236,11 @@
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>PLAQUENIL 200MG TAB</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-51502C4F7284</t>
         </is>
       </c>
@@ -18779,7 +19264,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18942,6 +19427,11 @@
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>ESIDREX TAB. 25 MG</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-D0984EE90629</t>
         </is>
       </c>
@@ -18965,7 +19455,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19128,6 +19618,11 @@
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>NEUROBION tablet</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-6773BADABB23</t>
         </is>
       </c>
@@ -19151,7 +19646,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19306,6 +19801,11 @@
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>ROBITUSSIN CF SYRUP</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-E521B299D507</t>
         </is>
       </c>
@@ -19329,7 +19829,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19499,6 +19999,11 @@
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>ACARIZAX 12SQ-HDM ORALLY LYOPHILISATE</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-6296B9C5D10C</t>
         </is>
@@ -19515,7 +20020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19561,100 +20066,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19686,7 +20196,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19701,92 +20211,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-16028</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>79.66</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>330</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19818,7 +20333,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19833,92 +20348,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-64021</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>442.96</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>331</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19950,7 +20470,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19965,92 +20485,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-31989</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>19.66</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>332</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20082,7 +20607,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20097,92 +20622,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-84994</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>250.45</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>333</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20214,7 +20744,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20229,92 +20759,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-75847</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>209.33</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>334</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20346,7 +20881,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20361,92 +20896,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-82753</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>52.96</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>335</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20478,7 +21018,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20493,92 +21033,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-99732</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>68.75</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>336</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20610,7 +21155,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20625,92 +21170,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-99785</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>146.18</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>337</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20742,7 +21292,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20757,92 +21307,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-24794</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>173.2</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>338</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20874,7 +21429,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20889,92 +21444,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-71381</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>446.77</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>339</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21006,7 +21566,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -21021,92 +21581,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-69458</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>124.64</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>340</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21123,7 +21688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21229,6 +21794,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21264,7 +21839,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21329,6 +21904,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-6D01DBA59E8F</t>
         </is>
@@ -21365,7 +21950,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21430,6 +22015,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-A82224E634C0</t>
         </is>
@@ -21466,7 +22061,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21531,6 +22126,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-D711610F414A</t>
         </is>
@@ -21567,7 +22172,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21632,6 +22237,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-6B5DC0DE0CF6</t>
         </is>
@@ -21668,7 +22283,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21733,6 +22348,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-F561CCE50077</t>
         </is>
@@ -21769,7 +22394,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21834,6 +22459,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-958D34E8BF37</t>
         </is>
@@ -21870,7 +22505,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21935,6 +22570,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-421494F5F6DF</t>
         </is>
@@ -21971,7 +22616,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -22036,6 +22681,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-E5B342FF3E7B</t>
         </is>
@@ -22072,7 +22727,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22137,6 +22792,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-125D2D3CC46F</t>
         </is>
@@ -22173,7 +22838,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22238,6 +22903,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-DA684349F88E</t>
         </is>
@@ -22274,7 +22949,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22339,6 +23014,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-0291A5A7AC5C</t>
         </is>
@@ -22375,7 +23060,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22440,6 +23125,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-F606F3089E8D</t>
         </is>
@@ -22476,7 +23171,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22541,6 +23236,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-A72877DE5C07</t>
         </is>
@@ -22577,7 +23282,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22642,6 +23347,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-96F76056050A</t>
         </is>
@@ -22678,7 +23393,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22743,6 +23458,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-80F54E11DEA7</t>
         </is>
@@ -22779,7 +23504,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22844,6 +23569,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-1CD4BED7C556</t>
         </is>
@@ -22880,7 +23615,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -22945,6 +23680,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-29A8456B2E09</t>
         </is>
@@ -22981,7 +23726,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -23046,6 +23791,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-B0745B3A907C</t>
         </is>
@@ -23082,7 +23837,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23147,6 +23902,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-947A7404379A</t>
         </is>
@@ -23183,7 +23948,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23248,6 +24013,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-2F2A09201441</t>
         </is>

--- a/product_upload/packages/38/file.xlsx
+++ b/product_upload/packages/38/file.xlsx
@@ -1490,8 +1490,16 @@
           <t>0823959219-858-661050536769</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ IRBEGEN PLUS 300/12.5 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>IRBEGEN PLUS 300/12.5 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
@@ -1685,8 +1693,16 @@
           <t>0367272924-783-191145200115</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SPEDRA 200 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>SPEDRA 200 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -1872,8 +1888,16 @@
           <t>2469716756-009-165532099484</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PANREST 20 mg Enteric Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>PANREST 20 mg Enteric Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -2063,8 +2087,16 @@
           <t>8124610376-425-009462026945</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PANREST 40 mg Enteric Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>PANREST 40 mg Enteric Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
@@ -2853,8 +2885,16 @@
           <t>7937898783-752-314014737507</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ QUET 100 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>QUET 100 mg Film-coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
@@ -3044,8 +3084,16 @@
           <t>8665458218-312-216333051631</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ QUET 200 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>QUET 200 mg Film-coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
@@ -3231,8 +3279,16 @@
           <t>8016801978-279-813744761207</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LUXAT 10mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>LUXAT 10mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
@@ -3621,8 +3677,16 @@
           <t>6090970240-977-925393277992</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ STEROFUNDIN ISO Solution For Infusion</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>STEROFUNDIN ISO Solution For Infusion detailed description.</t>
+        </is>
+      </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
@@ -3808,8 +3872,16 @@
           <t>7000759756-068-022761596939</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ STEROFUNDIN ISO Solution For Infusion</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>STEROFUNDIN ISO Solution For Infusion detailed description.</t>
+        </is>
+      </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
@@ -3995,8 +4067,16 @@
           <t>7561334494-169-883706963132</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SERCAND 200 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>SERCAND 200 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
@@ -4775,8 +4855,16 @@
           <t>0380283406-684-245162970284</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SERCAND 100 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>SERCAND 100 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
@@ -4962,8 +5050,16 @@
           <t>9562017688-276-934910039042</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SERCAND 300 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>SERCAND 300 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
@@ -5145,8 +5241,16 @@
           <t>1272632800-167-079823186595</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SUPRANE LIQUID FOR INHALATION</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>SUPRANE LIQUID FOR INHALATION detailed description.</t>
+        </is>
+      </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
@@ -5332,8 +5436,16 @@
           <t>7480207809-806-097810274688</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MIDIANA 3 mg/ 0.3 mg F.C.tablet</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>MIDIANA 3 mg/ 0.3 mg F.C.tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>AJA PHARMACEUTICAL INDUSTRIES</t>
@@ -5521,8 +5633,16 @@
           <t>9729874457-772-660527354432</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DAPO 60 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>DAPO 60 MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
@@ -5903,8 +6023,16 @@
           <t>2503703655-109-599081454712</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DIFLUCAN 200 mg capsule</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>DIFLUCAN 200 mg capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
@@ -6090,8 +6218,16 @@
           <t>5016965690-088-900352931880</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DIFLUCAN 50 mg capsule</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>DIFLUCAN 50 mg capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
@@ -7061,8 +7197,16 @@
           <t>1529142007-362-870654594654</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LIVADOR 750MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>LIVADOR 750MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
@@ -7443,8 +7587,16 @@
           <t>2899581476-239-049234496867</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SEIZET 100 mg Chewable/Dispersible Tablet</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>SEIZET 100 mg Chewable/Dispersible Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
@@ -7634,8 +7786,16 @@
           <t>3419514322-523-861903467351</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VIAGRA 50 mg Orodispersible Tablet</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>VIAGRA 50 mg Orodispersible Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
@@ -7825,8 +7985,16 @@
           <t>1036789405-144-491185866890</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZEIMER 10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>ZEIMER 10MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
@@ -8418,8 +8586,16 @@
           <t>7397143290-942-473327451763</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ENNLA 5% Cream</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>ENNLA 5% Cream detailed description.</t>
+        </is>
+      </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
@@ -9007,8 +9183,16 @@
           <t>0534437952-624-840542770786</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TARGINACT 10MG/5MG PR TABLET</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>TARGINACT 10MG/5MG PR TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
@@ -9194,8 +9378,16 @@
           <t>8039201983-200-425746338264</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OBSOL 5 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>OBSOL 5 MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr">
         <is>
           <t xml:space="preserve">MS Pharma Saudi </t>
@@ -9976,8 +10168,16 @@
           <t>4237352133-404-243183218837</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ QUREX XL 1000 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>QUREX XL 1000 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
@@ -10167,8 +10367,16 @@
           <t>2070450485-494-460910532189</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LIVADOR 500 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>LIVADOR 500 MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
@@ -10350,8 +10558,16 @@
           <t>5295908462-247-247965490561</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ROLITAC 5 mg Capsule</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>ROLITAC 5 mg Capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
@@ -10541,8 +10757,16 @@
           <t>7726149346-954-834898068652</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ROLITAC 0.5 mg Capsule</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>ROLITAC 0.5 mg Capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
@@ -10736,8 +10960,16 @@
           <t>4663153225-265-679145099099</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AXE BRAND UNIVERSAL OIL</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>AXE BRAND UNIVERSAL OIL detailed description.</t>
+        </is>
+      </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
@@ -10923,8 +11155,16 @@
           <t>0708698212-239-370829065524</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ROLITAC 1 mg Capsule</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>ROLITAC 1 mg Capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
@@ -11309,8 +11549,16 @@
           <t>3502361511-520-454735398924</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ METOJECT 50 mg/ml solution for injection</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>METOJECT 50 mg/ml solution for injection detailed description.</t>
+        </is>
+      </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
@@ -11496,8 +11744,16 @@
           <t>3561881871-212-119626094356</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TARGINACT 20MG/10MG PR TABLET</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>TARGINACT 20MG/10MG PR TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
@@ -11679,8 +11935,16 @@
           <t>6504317713-146-923124540182</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ANASTROZOLE 1MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>ANASTROZOLE 1MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
@@ -12274,8 +12538,16 @@
           <t>6368703376-545-658272701514</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OBSOL 10 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>OBSOL 10 MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr">
         <is>
           <t xml:space="preserve">MS Pharma Saudi </t>
@@ -12467,8 +12739,16 @@
           <t>6110095164-416-526652505299</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ REVCOX 200MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>REVCOX 200MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
@@ -12658,8 +12938,16 @@
           <t>8670727328-992-515872704067</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TARGINACT 40MG/20MG PR TABLET</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>TARGINACT 40MG/20MG PR TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
@@ -13440,8 +13728,16 @@
           <t>3929055345-150-015493005273</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ WELLBUTRIN XL 300 EXTENDED RELEASE F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>WELLBUTRIN XL 300 EXTENDED RELEASE F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
@@ -14817,8 +15113,16 @@
           <t>7275573317-291-219202192125</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DESCOVY 200MG/25MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>DESCOVY 200MG/25MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
@@ -15203,8 +15507,16 @@
           <t>2548560056-310-172932953060</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DIOZAD</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>DIOZAD detailed description.</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
           <t xml:space="preserve">Razy Al Madina Pharmaceutical	</t>
@@ -15591,8 +15903,16 @@
           <t>2802980717-008-274496404246</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ALZAMED 5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>ALZAMED 5MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
@@ -16377,8 +16697,16 @@
           <t>5305536933-515-299672298983</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LATUDA 40 MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>LATUDA 40 MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
@@ -16564,8 +16892,16 @@
           <t>1347377579-507-362045344308</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LETRASAN 2.5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>LETRASAN 2.5MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -16747,8 +17083,16 @@
           <t>5280192898-660-241555872591</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ELNASO 0.05% NASAL SPRAY</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>ELNASO 0.05% NASAL SPRAY detailed description.</t>
+        </is>
+      </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
@@ -16938,8 +17282,16 @@
           <t>5630187771-353-031603979887</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DESLORATADINE-GLENMARK 5MG TAB</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>DESLORATADINE-GLENMARK 5MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
@@ -17133,8 +17485,16 @@
           <t>9177494653-727-095025894712</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TORLEN 5 MG FILM-COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>TORLEN 5 MG FILM-COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -17320,8 +17680,16 @@
           <t>3252201740-182-635284888461</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NEULASTIM 6MG-0.6ML PRE-FILLED SYRINGE</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>NEULASTIM 6MG-0.6ML PRE-FILLED SYRINGE detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -18102,8 +18470,16 @@
           <t>4867417701-101-730782618273</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ANADEX 1MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>ANADEX 1MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr">
         <is>
           <t>Dallah Pharma Factory</t>
@@ -18299,8 +18675,16 @@
           <t>9723572661-932-987648007804</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RESINCALCIO POWDER FOR SUSPENSION</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>RESINCALCIO POWDER FOR SUSPENSION detailed description.</t>
+        </is>
+      </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
@@ -18490,8 +18874,16 @@
           <t>7461856738-808-333160345136</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CARBAGLU 200MG DISPERSIBLE TABLETS</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>CARBAGLU 200MG DISPERSIBLE TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
@@ -18884,8 +19276,16 @@
           <t>5950615834-528-933175338442</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ KYTRIL 1MG TAB</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>KYTRIL 1MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
@@ -19463,8 +19863,16 @@
           <t>9152069523-493-284557276551</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NEUROBION tablet</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>NEUROBION tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
@@ -19654,8 +20062,16 @@
           <t>1855646573-048-182568917759</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ROBITUSSIN CF SYRUP</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>ROBITUSSIN CF SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/38/file.xlsx
+++ b/product_upload/packages/38/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20482,7 +20482,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22104,7 +22104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22185,40 +22185,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22298,38 +22303,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>446.24</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-6D01DBA59E8F</t>
         </is>
@@ -22409,38 +22419,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>436.64</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-A82224E634C0</t>
         </is>
@@ -22520,38 +22535,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>498.28</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-D711610F414A</t>
         </is>
@@ -22631,38 +22651,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>265.99</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-6B5DC0DE0CF6</t>
         </is>
@@ -22742,38 +22767,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>139.9</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-F561CCE50077</t>
         </is>
@@ -22853,38 +22883,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>233.88</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-958D34E8BF37</t>
         </is>
@@ -22964,38 +22999,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>25.85</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-421494F5F6DF</t>
         </is>
@@ -23075,38 +23115,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>484.21</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-E5B342FF3E7B</t>
         </is>
@@ -23186,38 +23231,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>221</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-125D2D3CC46F</t>
         </is>
@@ -23297,38 +23347,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>396.71</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-DA684349F88E</t>
         </is>
@@ -23408,38 +23463,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>215.76</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-0291A5A7AC5C</t>
         </is>
@@ -23519,38 +23579,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>290.61</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-F606F3089E8D</t>
         </is>
@@ -23630,38 +23695,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>148.97</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-A72877DE5C07</t>
         </is>
@@ -23741,38 +23811,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>398.92</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-96F76056050A</t>
         </is>
@@ -23852,38 +23927,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>195.23</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-80F54E11DEA7</t>
         </is>
@@ -23963,38 +24043,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>236.93</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-1CD4BED7C556</t>
         </is>
@@ -24074,38 +24159,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>76.18000000000001</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-29A8456B2E09</t>
         </is>
@@ -24185,38 +24275,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>451.06</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-B0745B3A907C</t>
         </is>
@@ -24296,38 +24391,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>488.81</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-947A7404379A</t>
         </is>
@@ -24407,38 +24507,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>321.51</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-2F2A09201441</t>
         </is>
